--- a/NBFC-MF/Borrowers/Sanasam_Sonia_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Sanasam_Sonia_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>70</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>10000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>9247.0384022978469</v>
+        <v>4803.13010252807</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>10752.961597702153</v>
+        <v>15196.86989747193</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2957,703 +2957,753 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="2"/>
-      <c r="B72" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A72" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B72" s="23">
+        <f t="shared" si="12"/>
+        <v>71</v>
       </c>
       <c r="C72" s="3"/>
-      <c r="D72" s="4" t="str">
+      <c r="D72" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E72" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E72" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F72" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G72" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H72" s="4" t="str">
+        <v>28.796960046415869</v>
+      </c>
+      <c r="F72" s="4">
+        <f t="shared" si="14"/>
+        <v>171.20303995358412</v>
+      </c>
+      <c r="G72" s="4">
+        <f t="shared" si="13"/>
+        <v>9075.8353623442636</v>
+      </c>
+      <c r="H72" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>10924.164637655736</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="19"/>
-      <c r="B73" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A73" s="19">
+        <v>46216</v>
+      </c>
+      <c r="B73" s="24">
+        <f t="shared" si="12"/>
+        <v>72</v>
       </c>
       <c r="C73" s="20"/>
-      <c r="D73" s="21" t="str">
+      <c r="D73" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E73" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E73" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F73" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G73" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H73" s="21" t="str">
+        <v>28.263802630291892</v>
+      </c>
+      <c r="F73" s="21">
+        <f t="shared" si="14"/>
+        <v>171.73619736970812</v>
+      </c>
+      <c r="G73" s="21">
+        <f t="shared" si="13"/>
+        <v>8904.0991649745556</v>
+      </c>
+      <c r="H73" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>11095.900835025444</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="2"/>
-      <c r="B74" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A74" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B74" s="23">
+        <f t="shared" si="12"/>
+        <v>73</v>
       </c>
       <c r="C74" s="3"/>
-      <c r="D74" s="4" t="str">
+      <c r="D74" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E74" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E74" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F74" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G74" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H74" s="4" t="str">
+        <v>27.728984864968247</v>
+      </c>
+      <c r="F74" s="4">
+        <f t="shared" si="14"/>
+        <v>172.27101513503175</v>
+      </c>
+      <c r="G74" s="4">
+        <f t="shared" si="13"/>
+        <v>8731.8281498395245</v>
+      </c>
+      <c r="H74" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>11268.171850160476</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="19"/>
-      <c r="B75" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A75" s="19">
+        <v>46216</v>
+      </c>
+      <c r="B75" s="24">
+        <f t="shared" si="12"/>
+        <v>74</v>
       </c>
       <c r="C75" s="20"/>
-      <c r="D75" s="21" t="str">
+      <c r="D75" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E75" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E75" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F75" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G75" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H75" s="21" t="str">
+        <v>27.192501579815431</v>
+      </c>
+      <c r="F75" s="21">
+        <f t="shared" si="14"/>
+        <v>172.80749842018457</v>
+      </c>
+      <c r="G75" s="21">
+        <f t="shared" si="13"/>
+        <v>8559.0206514193396</v>
+      </c>
+      <c r="H75" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>11440.97934858066</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="2"/>
-      <c r="B76" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A76" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B76" s="23">
+        <f t="shared" si="12"/>
+        <v>75</v>
       </c>
       <c r="C76" s="3"/>
-      <c r="D76" s="4" t="str">
+      <c r="D76" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E76" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E76" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F76" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G76" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H76" s="4" t="str">
+        <v>26.654347588101658</v>
+      </c>
+      <c r="F76" s="4">
+        <f t="shared" si="14"/>
+        <v>173.34565241189836</v>
+      </c>
+      <c r="G76" s="4">
+        <f t="shared" si="13"/>
+        <v>8385.6749990074404</v>
+      </c>
+      <c r="H76" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>11614.32500099256</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="19"/>
-      <c r="B77" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A77" s="19">
+        <v>46216</v>
+      </c>
+      <c r="B77" s="24">
+        <f t="shared" si="12"/>
+        <v>76</v>
       </c>
       <c r="C77" s="20"/>
-      <c r="D77" s="21" t="str">
+      <c r="D77" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E77" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E77" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F77" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G77" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H77" s="21" t="str">
+        <v>26.114517686942719</v>
+      </c>
+      <c r="F77" s="21">
+        <f t="shared" si="14"/>
+        <v>173.88548231305728</v>
+      </c>
+      <c r="G77" s="21">
+        <f t="shared" si="13"/>
+        <v>8211.7895166943836</v>
+      </c>
+      <c r="H77" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>11788.210483305616</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="2"/>
-      <c r="B78" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A78" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B78" s="23">
+        <f t="shared" si="12"/>
+        <v>77</v>
       </c>
       <c r="C78" s="3"/>
-      <c r="D78" s="4" t="str">
+      <c r="D78" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E78" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E78" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F78" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G78" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H78" s="4" t="str">
+        <v>25.573006657251685</v>
+      </c>
+      <c r="F78" s="4">
+        <f t="shared" si="14"/>
+        <v>174.42699334274832</v>
+      </c>
+      <c r="G78" s="4">
+        <f t="shared" si="13"/>
+        <v>8037.362523351635</v>
+      </c>
+      <c r="H78" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>11962.637476648364</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="19"/>
-      <c r="B79" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A79" s="19">
+        <v>46216</v>
+      </c>
+      <c r="B79" s="24">
+        <f t="shared" si="12"/>
+        <v>78</v>
       </c>
       <c r="C79" s="20"/>
-      <c r="D79" s="21" t="str">
+      <c r="D79" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E79" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E79" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F79" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G79" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H79" s="21" t="str">
+        <v>25.029809263688424</v>
+      </c>
+      <c r="F79" s="21">
+        <f t="shared" si="14"/>
+        <v>174.97019073631157</v>
+      </c>
+      <c r="G79" s="21">
+        <f t="shared" si="13"/>
+        <v>7862.3923326153235</v>
+      </c>
+      <c r="H79" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>12137.607667384676</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="2"/>
-      <c r="B80" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A80" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B80" s="23">
+        <f t="shared" si="12"/>
+        <v>79</v>
       </c>
       <c r="C80" s="3"/>
-      <c r="D80" s="4" t="str">
+      <c r="D80" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E80" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E80" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F80" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G80" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H80" s="4" t="str">
+        <v>24.484920254609012</v>
+      </c>
+      <c r="F80" s="4">
+        <f t="shared" si="14"/>
+        <v>175.51507974539098</v>
+      </c>
+      <c r="G80" s="4">
+        <f t="shared" si="13"/>
+        <v>7686.8772528699328</v>
+      </c>
+      <c r="H80" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>12313.122747130066</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="19"/>
-      <c r="B81" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A81" s="19">
+        <v>46216</v>
+      </c>
+      <c r="B81" s="24">
+        <f t="shared" si="12"/>
+        <v>80</v>
       </c>
       <c r="C81" s="20"/>
-      <c r="D81" s="21" t="str">
+      <c r="D81" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E81" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E81" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F81" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G81" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H81" s="21" t="str">
+        <v>23.938334362014956</v>
+      </c>
+      <c r="F81" s="21">
+        <f t="shared" si="14"/>
+        <v>176.06166563798504</v>
+      </c>
+      <c r="G81" s="21">
+        <f t="shared" si="13"/>
+        <v>7510.8155872319476</v>
+      </c>
+      <c r="H81" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>12489.184412768052</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="2"/>
-      <c r="B82" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A82" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B82" s="23">
+        <f t="shared" si="12"/>
+        <v>81</v>
       </c>
       <c r="C82" s="3"/>
-      <c r="D82" s="4" t="str">
+      <c r="D82" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E82" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E82" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F82" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G82" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H82" s="4" t="str">
+        <v>23.390046301502238</v>
+      </c>
+      <c r="F82" s="4">
+        <f t="shared" si="14"/>
+        <v>176.60995369849775</v>
+      </c>
+      <c r="G82" s="4">
+        <f t="shared" si="13"/>
+        <v>7334.2056335334501</v>
+      </c>
+      <c r="H82" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>12665.794366466551</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="19"/>
-      <c r="B83" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A83" s="19">
+        <v>46216</v>
+      </c>
+      <c r="B83" s="24">
+        <f t="shared" si="12"/>
+        <v>82</v>
       </c>
       <c r="C83" s="20"/>
-      <c r="D83" s="21" t="str">
+      <c r="D83" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E83" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E83" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F83" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G83" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H83" s="21" t="str">
+        <v>22.840050772210269</v>
+      </c>
+      <c r="F83" s="21">
+        <f t="shared" si="14"/>
+        <v>177.15994922778972</v>
+      </c>
+      <c r="G83" s="21">
+        <f t="shared" si="13"/>
+        <v>7157.04568430566</v>
+      </c>
+      <c r="H83" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>12842.95431569434</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="2"/>
-      <c r="B84" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A84" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B84" s="23">
+        <f t="shared" si="12"/>
+        <v>83</v>
       </c>
       <c r="C84" s="3"/>
-      <c r="D84" s="4" t="str">
+      <c r="D84" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E84" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E84" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F84" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G84" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H84" s="4" t="str">
+        <v>22.288342456770593</v>
+      </c>
+      <c r="F84" s="4">
+        <f t="shared" si="14"/>
+        <v>177.71165754322942</v>
+      </c>
+      <c r="G84" s="4">
+        <f t="shared" si="13"/>
+        <v>6979.3340267624308</v>
+      </c>
+      <c r="H84" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>13020.66597323757</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="19"/>
-      <c r="B85" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A85" s="19">
+        <v>46216</v>
+      </c>
+      <c r="B85" s="24">
+        <f t="shared" si="12"/>
+        <v>84</v>
       </c>
       <c r="C85" s="20"/>
-      <c r="D85" s="21" t="str">
+      <c r="D85" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E85" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E85" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F85" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G85" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H85" s="21" t="str">
+        <v>21.734916021255518</v>
+      </c>
+      <c r="F85" s="21">
+        <f t="shared" si="14"/>
+        <v>178.26508397874449</v>
+      </c>
+      <c r="G85" s="21">
+        <f t="shared" si="13"/>
+        <v>6801.068942783686</v>
+      </c>
+      <c r="H85" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>13198.931057216314</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="2"/>
-      <c r="B86" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A86" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B86" s="23">
+        <f t="shared" si="12"/>
+        <v>85</v>
       </c>
       <c r="C86" s="3"/>
-      <c r="D86" s="4" t="str">
+      <c r="D86" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E86" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E86" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F86" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G86" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H86" s="4" t="str">
+        <v>21.179766115126519</v>
+      </c>
+      <c r="F86" s="4">
+        <f t="shared" si="14"/>
+        <v>178.82023388487349</v>
+      </c>
+      <c r="G86" s="4">
+        <f t="shared" si="13"/>
+        <v>6622.2487088988128</v>
+      </c>
+      <c r="H86" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>13377.751291101187</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="19"/>
-      <c r="B87" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A87" s="19">
+        <v>46216</v>
+      </c>
+      <c r="B87" s="24">
+        <f t="shared" si="12"/>
+        <v>86</v>
       </c>
       <c r="C87" s="20"/>
-      <c r="D87" s="21" t="str">
+      <c r="D87" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E87" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E87" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F87" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G87" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H87" s="21" t="str">
+        <v>20.622887371182532</v>
+      </c>
+      <c r="F87" s="21">
+        <f t="shared" si="14"/>
+        <v>179.37711262881746</v>
+      </c>
+      <c r="G87" s="21">
+        <f t="shared" si="13"/>
+        <v>6442.8715962699953</v>
+      </c>
+      <c r="H87" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>13557.128403730005</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="2"/>
-      <c r="B88" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A88" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B88" s="23">
+        <f t="shared" si="12"/>
+        <v>87</v>
       </c>
       <c r="C88" s="3"/>
-      <c r="D88" s="4" t="str">
+      <c r="D88" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E88" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E88" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F88" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G88" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H88" s="4" t="str">
+        <v>20.064274405508044</v>
+      </c>
+      <c r="F88" s="4">
+        <f t="shared" si="14"/>
+        <v>179.93572559449194</v>
+      </c>
+      <c r="G88" s="4">
+        <f t="shared" si="13"/>
+        <v>6262.9358706755029</v>
+      </c>
+      <c r="H88" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>13737.064129324497</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="19"/>
-      <c r="B89" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A89" s="19">
+        <v>46216</v>
+      </c>
+      <c r="B89" s="24">
+        <f t="shared" si="12"/>
+        <v>88</v>
       </c>
       <c r="C89" s="20"/>
-      <c r="D89" s="21" t="str">
+      <c r="D89" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E89" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E89" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F89" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G89" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H89" s="21" t="str">
+        <v>19.503921817421045</v>
+      </c>
+      <c r="F89" s="21">
+        <f t="shared" si="14"/>
+        <v>180.49607818257897</v>
+      </c>
+      <c r="G89" s="21">
+        <f t="shared" si="13"/>
+        <v>6082.4397924929235</v>
+      </c>
+      <c r="H89" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>13917.560207507076</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="2"/>
-      <c r="B90" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A90" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B90" s="23">
+        <f t="shared" si="12"/>
+        <v>89</v>
       </c>
       <c r="C90" s="3"/>
-      <c r="D90" s="4" t="str">
+      <c r="D90" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E90" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E90" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F90" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G90" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H90" s="4" t="str">
+        <v>18.941824189420835</v>
+      </c>
+      <c r="F90" s="4">
+        <f t="shared" si="14"/>
+        <v>181.05817581057917</v>
+      </c>
+      <c r="G90" s="4">
+        <f t="shared" si="13"/>
+        <v>5901.3816166823444</v>
+      </c>
+      <c r="H90" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>14098.618383317655</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="19"/>
-      <c r="B91" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A91" s="19">
+        <v>46216</v>
+      </c>
+      <c r="B91" s="24">
+        <f t="shared" si="12"/>
+        <v>90</v>
       </c>
       <c r="C91" s="20"/>
-      <c r="D91" s="21" t="str">
+      <c r="D91" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E91" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E91" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F91" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G91" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H91" s="21" t="str">
+        <v>18.377976087135615</v>
+      </c>
+      <c r="F91" s="21">
+        <f t="shared" si="14"/>
+        <v>181.62202391286439</v>
+      </c>
+      <c r="G91" s="21">
+        <f t="shared" si="13"/>
+        <v>5719.7595927694802</v>
+      </c>
+      <c r="H91" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>14280.24040723052</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="2"/>
-      <c r="B92" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A92" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B92" s="23">
+        <f t="shared" si="12"/>
+        <v>91</v>
       </c>
       <c r="C92" s="3"/>
-      <c r="D92" s="4" t="str">
+      <c r="D92" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E92" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E92" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F92" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G92" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H92" s="4" t="str">
+        <v>17.812372059269972</v>
+      </c>
+      <c r="F92" s="4">
+        <f t="shared" si="14"/>
+        <v>182.18762794073004</v>
+      </c>
+      <c r="G92" s="4">
+        <f t="shared" si="13"/>
+        <v>5537.5719648287504</v>
+      </c>
+      <c r="H92" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>14462.42803517125</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="19"/>
-      <c r="B93" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A93" s="19">
+        <v>46216</v>
+      </c>
+      <c r="B93" s="24">
+        <f t="shared" si="12"/>
+        <v>92</v>
       </c>
       <c r="C93" s="20"/>
-      <c r="D93" s="21" t="str">
+      <c r="D93" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E93" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E93" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F93" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G93" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H93" s="21" t="str">
+        <v>17.245006637552166</v>
+      </c>
+      <c r="F93" s="21">
+        <f t="shared" si="14"/>
+        <v>182.75499336244783</v>
+      </c>
+      <c r="G93" s="21">
+        <f t="shared" si="13"/>
+        <v>5354.8169714663027</v>
+      </c>
+      <c r="H93" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>14645.183028533698</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="2"/>
-      <c r="B94" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A94" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B94" s="23">
+        <f t="shared" si="12"/>
+        <v>93</v>
       </c>
       <c r="C94" s="3"/>
-      <c r="D94" s="4" t="str">
+      <c r="D94" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E94" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E94" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F94" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G94" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H94" s="4" t="str">
+        <v>16.675874336681257</v>
+      </c>
+      <c r="F94" s="4">
+        <f t="shared" si="14"/>
+        <v>183.32412566331874</v>
+      </c>
+      <c r="G94" s="4">
+        <f t="shared" si="13"/>
+        <v>5171.4928458029835</v>
+      </c>
+      <c r="H94" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>14828.507154197017</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="19"/>
-      <c r="B95" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A95" s="19">
+        <v>46216</v>
+      </c>
+      <c r="B95" s="24">
+        <f t="shared" si="12"/>
+        <v>94</v>
       </c>
       <c r="C95" s="20"/>
-      <c r="D95" s="21" t="str">
+      <c r="D95" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E95" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E95" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F95" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G95" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H95" s="21" t="str">
+        <v>16.104969654274093</v>
+      </c>
+      <c r="F95" s="21">
+        <f t="shared" si="14"/>
+        <v>183.8950303457259</v>
+      </c>
+      <c r="G95" s="21">
+        <f t="shared" si="13"/>
+        <v>4987.5978154572576</v>
+      </c>
+      <c r="H95" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>15012.402184542741</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="2"/>
-      <c r="B96" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A96" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B96" s="23">
+        <f t="shared" si="12"/>
+        <v>95</v>
       </c>
       <c r="C96" s="3"/>
-      <c r="D96" s="4" t="str">
+      <c r="D96" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E96" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E96" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F96" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G96" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H96" s="4" t="str">
+        <v>15.532287070812087</v>
+      </c>
+      <c r="F96" s="4">
+        <f t="shared" si="14"/>
+        <v>184.46771292918791</v>
+      </c>
+      <c r="G96" s="4">
+        <f t="shared" si="13"/>
+        <v>4803.13010252807</v>
+      </c>
+      <c r="H96" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>15196.86989747193</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Sanasam_Sonia_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Sanasam_Sonia_Daily.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Loan1" sheetId="4" r:id="rId1"/>

--- a/NBFC-MF/Borrowers/Sanasam_Sonia_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Sanasam_Sonia_Daily.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Loan1" sheetId="4" r:id="rId1"/>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>5000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>4803.13010252807</v>
+        <v>3872.1386840566906</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>15196.86989747193</v>
+        <v>16127.86131594331</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -3707,143 +3707,153 @@
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="19"/>
-      <c r="B97" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A97" s="19">
+        <v>46249</v>
+      </c>
+      <c r="B97" s="24">
+        <f t="shared" si="12"/>
+        <v>96</v>
       </c>
       <c r="C97" s="20"/>
-      <c r="D97" s="21" t="str">
+      <c r="D97" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E97" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E97" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F97" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G97" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H97" s="21" t="str">
+        <v>14.957821049587876</v>
+      </c>
+      <c r="F97" s="21">
+        <f t="shared" si="14"/>
+        <v>185.04217895041214</v>
+      </c>
+      <c r="G97" s="21">
+        <f t="shared" si="13"/>
+        <v>4618.0879235776574</v>
+      </c>
+      <c r="H97" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>15381.912076422343</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="2"/>
-      <c r="B98" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A98" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B98" s="23">
+        <f t="shared" si="12"/>
+        <v>97</v>
       </c>
       <c r="C98" s="3"/>
-      <c r="D98" s="4" t="str">
+      <c r="D98" s="4">
         <f t="shared" ref="D98:D121" si="15">IF(AND($A98&lt;&gt;"",$B98&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E98" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E98" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F98" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G98" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H98" s="4" t="str">
+        <v>14.381566036651776</v>
+      </c>
+      <c r="F98" s="4">
+        <f t="shared" si="14"/>
+        <v>185.61843396334822</v>
+      </c>
+      <c r="G98" s="4">
+        <f t="shared" si="13"/>
+        <v>4432.4694896143092</v>
+      </c>
+      <c r="H98" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>15567.530510385692</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="19"/>
-      <c r="B99" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A99" s="19">
+        <v>46249</v>
+      </c>
+      <c r="B99" s="24">
+        <f t="shared" si="12"/>
+        <v>98</v>
       </c>
       <c r="C99" s="20"/>
-      <c r="D99" s="21" t="str">
+      <c r="D99" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E99" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E99" s="21">
         <f t="shared" ref="E99:E121" si="16">IF(AND($A99&lt;&gt;"",$B99&lt;&gt;""),G98*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F99" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G99" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H99" s="21" t="str">
+        <v>13.803516460758098</v>
+      </c>
+      <c r="F99" s="21">
+        <f t="shared" si="14"/>
+        <v>186.19648353924191</v>
+      </c>
+      <c r="G99" s="21">
+        <f t="shared" si="13"/>
+        <v>4246.2730060750673</v>
+      </c>
+      <c r="H99" s="21">
         <f t="shared" ref="H99:H121" si="17">IF(AND($A99&lt;&gt;"",$B99&lt;&gt;""),$K$7-G99,"")</f>
-        <v/>
+        <v>15753.726993924933</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="2"/>
-      <c r="B100" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A100" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B100" s="23">
+        <f t="shared" si="12"/>
+        <v>99</v>
       </c>
       <c r="C100" s="3"/>
-      <c r="D100" s="4" t="str">
+      <c r="D100" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E100" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E100" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F100" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G100" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H100" s="4" t="str">
+        <v>13.223666733311278</v>
+      </c>
+      <c r="F100" s="4">
+        <f t="shared" si="14"/>
+        <v>186.77633326668871</v>
+      </c>
+      <c r="G100" s="4">
+        <f t="shared" si="13"/>
+        <v>4059.4966728083787</v>
+      </c>
+      <c r="H100" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>15940.503327191622</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="19"/>
-      <c r="B101" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A101" s="19">
+        <v>46249</v>
+      </c>
+      <c r="B101" s="24">
+        <f t="shared" si="12"/>
+        <v>100</v>
       </c>
       <c r="C101" s="20"/>
-      <c r="D101" s="21" t="str">
+      <c r="D101" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E101" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E101" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F101" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G101" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H101" s="21" t="str">
+        <v>12.642011248311851</v>
+      </c>
+      <c r="F101" s="21">
+        <f t="shared" si="14"/>
+        <v>187.35798875168814</v>
+      </c>
+      <c r="G101" s="21">
+        <f t="shared" si="13"/>
+        <v>3872.1386840566906</v>
+      </c>
+      <c r="H101" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>16127.86131594331</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Sanasam_Sonia_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Sanasam_Sonia_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>4000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>3872.1386840566906</v>
+        <v>2926.5603118846607</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>16127.86131594331</v>
+        <v>17073.439688115341</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -3857,143 +3857,153 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="2"/>
-      <c r="B102" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A102" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B102" s="23">
+        <f t="shared" si="12"/>
+        <v>101</v>
       </c>
       <c r="C102" s="3"/>
-      <c r="D102" s="4" t="str">
+      <c r="D102" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E102" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E102" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F102" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G102" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H102" s="4" t="str">
+        <v>12.058544382302246</v>
+      </c>
+      <c r="F102" s="4">
+        <f t="shared" si="14"/>
+        <v>187.94145561769776</v>
+      </c>
+      <c r="G102" s="4">
+        <f t="shared" si="13"/>
+        <v>3684.1972284389931</v>
+      </c>
+      <c r="H102" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>16315.802771561008</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="19"/>
-      <c r="B103" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A103" s="19">
+        <v>46259</v>
+      </c>
+      <c r="B103" s="24">
+        <f t="shared" si="12"/>
+        <v>102</v>
       </c>
       <c r="C103" s="20"/>
-      <c r="D103" s="21" t="str">
+      <c r="D103" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E103" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E103" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F103" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G103" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H103" s="21" t="str">
+        <v>11.473260494312424</v>
+      </c>
+      <c r="F103" s="21">
+        <f t="shared" si="14"/>
+        <v>188.52673950568757</v>
+      </c>
+      <c r="G103" s="21">
+        <f t="shared" si="13"/>
+        <v>3495.6704889333055</v>
+      </c>
+      <c r="H103" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>16504.329511066695</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="2"/>
-      <c r="B104" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A104" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B104" s="23">
+        <f t="shared" si="12"/>
+        <v>103</v>
       </c>
       <c r="C104" s="3"/>
-      <c r="D104" s="4" t="str">
+      <c r="D104" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E104" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E104" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F104" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G104" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H104" s="4" t="str">
+        <v>10.886153925805337</v>
+      </c>
+      <c r="F104" s="4">
+        <f t="shared" si="14"/>
+        <v>189.11384607419467</v>
+      </c>
+      <c r="G104" s="4">
+        <f t="shared" si="13"/>
+        <v>3306.556642859111</v>
+      </c>
+      <c r="H104" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>16693.443357140888</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="19"/>
-      <c r="B105" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A105" s="19">
+        <v>46259</v>
+      </c>
+      <c r="B105" s="24">
+        <f t="shared" si="12"/>
+        <v>104</v>
       </c>
       <c r="C105" s="20"/>
-      <c r="D105" s="21" t="str">
+      <c r="D105" s="21">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E105" s="21" t="str">
+        <v>200</v>
+      </c>
+      <c r="E105" s="21">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F105" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G105" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H105" s="21" t="str">
+        <v>10.297219000622228</v>
+      </c>
+      <c r="F105" s="21">
+        <f t="shared" si="14"/>
+        <v>189.70278099937778</v>
+      </c>
+      <c r="G105" s="21">
+        <f t="shared" si="13"/>
+        <v>3116.8538618597331</v>
+      </c>
+      <c r="H105" s="21">
         <f t="shared" si="17"/>
-        <v/>
+        <v>16883.146138140266</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="2"/>
-      <c r="B106" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A106" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B106" s="23">
+        <f t="shared" si="12"/>
+        <v>105</v>
       </c>
       <c r="C106" s="3"/>
-      <c r="D106" s="4" t="str">
+      <c r="D106" s="4">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="E106" s="4" t="str">
+        <v>200</v>
+      </c>
+      <c r="E106" s="4">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="F106" s="4" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="G106" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H106" s="4" t="str">
+        <v>9.7064500249277437</v>
+      </c>
+      <c r="F106" s="4">
+        <f t="shared" si="14"/>
+        <v>190.29354997507227</v>
+      </c>
+      <c r="G106" s="4">
+        <f t="shared" si="13"/>
+        <v>2926.5603118846607</v>
+      </c>
+      <c r="H106" s="4">
         <f t="shared" si="17"/>
-        <v/>
+        <v>17073.439688115341</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
